--- a/eoe/Assets/Excels/SpawnConfig.xlsx
+++ b/eoe/Assets/Excels/SpawnConfig.xlsx
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
@@ -544,10 +544,10 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
@@ -575,10 +575,10 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
@@ -606,10 +606,10 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
@@ -637,10 +637,10 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -978,10 +978,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C17" t="n">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C19" t="n">
-        <v>34</v>
+        <v>136</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="C20" t="n">
-        <v>42</v>
+        <v>168</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C21" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C22" t="n">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="C23" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="C24" t="n">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C25" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="C26" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C29" t="n">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C30" t="n">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C32" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C33" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C34" t="n">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C35" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C36" t="n">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C37" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1660,10 +1660,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C39" t="n">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C40" t="n">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C41" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C42" t="n">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C43" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1815,10 +1815,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C44" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C45" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C46" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C47" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1970,10 +1970,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C49" t="n">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C50" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C52" t="n">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C54" t="n">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C55" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C56" t="n">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C57" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C59" t="n">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C60" t="n">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C62" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C63" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C64" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C65" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C66" t="n">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C67" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C69" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C70" t="n">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C71" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C72" t="n">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C73" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C74" t="n">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C75" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C76" t="n">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C77" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C79" t="n">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C80" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C81" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C82" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C83" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C84" t="n">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C85" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C86" t="n">
-        <v>29</v>
+        <v>116</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C87" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -3210,10 +3210,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C89" t="n">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C90" t="n">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C91" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C92" t="n">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C93" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C94" t="n">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C95" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C96" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C97" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C99" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C100" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C101" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C102" t="n">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C103" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C104" t="n">
-        <v>29</v>
+        <v>116</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C105" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -3737,10 +3737,10 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C106" t="n">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C107" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="C108" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C109" t="n">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C110" t="n">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C111" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -3923,10 +3923,10 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C112" t="n">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C113" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -3985,10 +3985,10 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C114" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C115" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -4047,10 +4047,10 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C116" t="n">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C117" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -4109,10 +4109,10 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="C118" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -4140,10 +4140,10 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C119" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C120" t="n">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C121" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C122" t="n">
-        <v>29</v>
+        <v>116</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -4264,10 +4264,10 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C123" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C124" t="n">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -4326,10 +4326,10 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C125" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C126" t="n">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C127" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="C128" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -4450,10 +4450,10 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C129" t="n">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C130" t="n">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -4512,10 +4512,10 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C131" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -4543,10 +4543,10 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C132" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C133" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C134" t="n">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C135" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C136" t="n">
-        <v>34</v>
+        <v>136</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C137" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -4729,10 +4729,10 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="C138" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -4760,10 +4760,10 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C139" t="n">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -4791,10 +4791,10 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C140" t="n">
-        <v>29</v>
+        <v>116</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C141" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C142" t="n">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C143" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C144" t="n">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C145" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C146" t="n">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C147" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="C148" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -5070,10 +5070,10 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C149" t="n">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C150" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -5132,10 +5132,10 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C151" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -5163,10 +5163,10 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C152" t="n">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C153" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C154" t="n">
-        <v>34</v>
+        <v>136</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -5256,10 +5256,10 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C155" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -5287,10 +5287,10 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C156" t="n">
-        <v>36</v>
+        <v>144</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C157" t="n">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -5349,10 +5349,10 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="C158" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C159" t="n">
-        <v>29</v>
+        <v>116</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C160" t="n">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -5442,10 +5442,10 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C161" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C162" t="n">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C163" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -5535,10 +5535,10 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C164" t="n">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -5566,10 +5566,10 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C165" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C166" t="n">
-        <v>37</v>
+        <v>148</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -5628,10 +5628,10 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C167" t="n">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -5659,10 +5659,10 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="C168" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -5690,10 +5690,10 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C169" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -5721,10 +5721,10 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C170" t="n">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -5752,10 +5752,10 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C171" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C172" t="n">
-        <v>34</v>
+        <v>136</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C173" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -5845,10 +5845,10 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C174" t="n">
-        <v>36</v>
+        <v>144</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C175" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -5907,10 +5907,10 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="C176" t="n">
-        <v>38</v>
+        <v>152</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="C177" t="n">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -5969,10 +5969,10 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="C178" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
